--- a/public/plantilla-cal-vaciado.xlsx
+++ b/public/plantilla-cal-vaciado.xlsx
@@ -12537,7 +12537,7 @@
         <v/>
       </c>
       <c r="G37" s="135">
-        <f>COUNT(B27:B36)&amp;" camiones"</f>
+        <f>COUNTA(B27:B36)&amp;" camiones"</f>
         <v/>
       </c>
       <c r="H37" s="32" t="n"/>
